--- a/12-opakovani/otázky ke zkoušce.xlsx
+++ b/12-opakovani/otázky ke zkoušce.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\4iz160-cviceni\12-opakovani\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Standa\Work\Výuka\4iz160\12-opakovani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06997CB-7019-429C-AF17-56372A82C515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C27656-EF8C-4920-9617-78731F590CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{4CE46129-BC7A-42C7-9A36-170690D1E201}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4CE46129-BC7A-42C7-9A36-170690D1E201}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
   <si>
     <t>Téma</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Upřesnění</t>
   </si>
   <si>
-    <t>Pořadí</t>
-  </si>
-  <si>
     <t>Strukturované datové formáty</t>
   </si>
   <si>
@@ -54,18 +51,6 @@
     <t>Jakým způsobem se dá popsat struktura XML dokumentu? Co je to xpath? Kde se XML používá? Mohu si vytvořit vlastní XML formát? Zkuste najít nějaký příklad XML dokumentu volně dostupného přes internet.</t>
   </si>
   <si>
-    <t>SOA</t>
-  </si>
-  <si>
-    <t>Využívání IT služeb</t>
-  </si>
-  <si>
-    <t>Základní vlastnosti API</t>
-  </si>
-  <si>
-    <t>Co je to API? K čemu se používá? Stručně popište rozdíl mezi SOAP, REST API a GraphQL</t>
-  </si>
-  <si>
     <t>K čemu slouží protokol HTTP? Jaké jeho verze se v současné době používají? Jaký je rozdíl mezi HTTP a HTTPS? Je možné mít API postavené i na jiném protokolu, než http/https?</t>
   </si>
   <si>
@@ -78,42 +63,6 @@
     <t>Jaké jsou základní vlastnosti protokolu http/https? Má použití HTTPS vliv na SEO? Jaké typy požadavků je možné v protokolu HTTP využívat? Uveďte příklad hlaviček v požadavku a v odpovědi zaslané přes HTTP/HTTPS.</t>
   </si>
   <si>
-    <t>XML-RPC, SOAP</t>
-  </si>
-  <si>
-    <t>SOAP - WSDL</t>
-  </si>
-  <si>
-    <t>Co je to WSDL? V jakých programovacích jazycích lze využítat web services (SOAP)? Jaké jsou základní vlastnosti SOAP API? Jaký datový formát se používá pro přenos dat přes SOAP?</t>
-  </si>
-  <si>
-    <t>Co je to XML-RPC? Co je to SOAP a k čemu se používá? Zvládl(a) byste najít nějaký příklad použití tohoto typu API? Jakým způsobem lze dokumentovat API tohoto typu?</t>
-  </si>
-  <si>
-    <t>gRPC</t>
-  </si>
-  <si>
-    <t>REST API</t>
-  </si>
-  <si>
-    <t>Jaké jsou vlastnosti REST API? Jaký formát dat se přenáší protokolem REST? Charakterizujte vazbu REST API a HTTP. Pokuste se najít nějakou ukázku praktického využití REST API.</t>
-  </si>
-  <si>
-    <t>REST API, OpenAPI</t>
-  </si>
-  <si>
-    <t>Co je to OpenAPI? Charakterizujte vztahu OpenAPI a RESTu. Jakým způsobem lze provést autentizaci uživatele tohoto API? Co označujeme v REST API jako zdroj? Jaké operace jdou se zdrojem provádět?</t>
-  </si>
-  <si>
-    <t>Prototypování REST API, JSON:API</t>
-  </si>
-  <si>
-    <t>Jaké nástroje se používají pro dokumentaci a pro prototypování REST API? K čemu je vlastně dobré vytvářet prototyp REST API? Charakterizujte JSON:API, jeho vlastnosti a použití.</t>
-  </si>
-  <si>
-    <t>Zkuste popsat vlastnosti gRPC a možnosti jeho použití. Co mají společného gRPC a SOAP? Co jsou to "protocol buffers"? Našel/našla byste nějaký příklad implementace?</t>
-  </si>
-  <si>
     <t>GraphQL</t>
   </si>
   <si>
@@ -123,33 +72,15 @@
     <t>Grafová data</t>
   </si>
   <si>
-    <t>Co jsou to grafová data? Jaký je vztah grafových dat a GraphQL? Je možné najít grafová data např. na Facebooku? Lze se dotazovat na grafová data přes REST API?</t>
-  </si>
-  <si>
     <t>Integrační služby, API v aplikacích</t>
   </si>
   <si>
-    <t>Lze najít API i v aplikacích, které mají vlastní uživatelské rozhraní? K čemu se používají integrační služby? Vyberte si nějakou integrační službu a popište její vlastnosti a nějaké vhodné příklady použití.</t>
-  </si>
-  <si>
-    <t>Jaký je vztah dat, informací a znalostí? Co jsou to explicitní a tacitní znalosti? Lze znalosti někde shromažďovat a nějak je sdílet a prohledávat? Mají informace a znalosti nějakou hodnotu?</t>
-  </si>
-  <si>
     <t>Data - informace - znalosti</t>
   </si>
   <si>
-    <t>Informační zdroje</t>
-  </si>
-  <si>
-    <t>Co je to "informační zdroj"? Co jsou to primární, sekundární a terciání informace? Co je to informační hodnota dat? Jaké jsou způsoby zaznamenávání informací?</t>
-  </si>
-  <si>
     <t>Strukturovaná a nestrukturovaná data, informační zdroje</t>
   </si>
   <si>
-    <t>Jaké jsou výhody a nevýhody jednotlivých variant uložení dat? V jakých formátech se obvykle sdílejí data v prostředí internetu? Jak poznat relevantní informační zdroj?</t>
-  </si>
-  <si>
     <t>Vyhledávání</t>
   </si>
   <si>
@@ -162,51 +93,12 @@
     <t>Popište proces vyhledávání informací ve více informačních zdrojích najednou. Je nutné opravdu odeslat dotaz všem databázím najednou? Popište výhody a nevýhody centralizovaného a distribuovaného modelu vyhledávání. Co je to deduplikace a obohacování výsledků?</t>
   </si>
   <si>
-    <t>Přístup ke zdrojům</t>
-  </si>
-  <si>
-    <t>Přístup ke zdrojům v knihovnách</t>
-  </si>
-  <si>
-    <t>Jakým způsobem lze získávat dokumenty z knihoven? Lze např. naší školní knihovně předložit požadavek na zjištění konkrétní informace? Co knihovny obvykle označují jako "elektronické informační zdroje"? Jakým způsobem lze popsat dokumenty zpracovávané knihovnami?</t>
-  </si>
-  <si>
     <t>Data a metadata</t>
   </si>
   <si>
-    <t>K čemu se používají metadata? Jaký je vztah dat a metadat? Charakterizujte metadata informačních zdrojů. Co je to formát MARC?</t>
-  </si>
-  <si>
-    <t>Metadata na internetu</t>
-  </si>
-  <si>
-    <t>Jaká metadat se na používají u webových stránek? K čemu tato metadata slouží? Co jsou to sémantická data na webu a co mají společného s schema.org? Co je to OpenGraph? Uveďte příklady použití.</t>
-  </si>
-  <si>
-    <t>Modely fungování informačních systémů</t>
-  </si>
-  <si>
-    <t>Stručně uveďte, co je to funkční, procesní a technologická architektura IS. Jaký je rozdíl mezi centralizovaným a distribuovaným modelem integrace informačních zdrojů do jednoho informačního systému? Co je to choreografie a orchestrace služeb?</t>
-  </si>
-  <si>
-    <t>Portály, mashup aplikace</t>
-  </si>
-  <si>
-    <t>Co je to portál? Uveďte příklad portálů. Co zajišťuje portál pro jednotlivé portlety? Je každý dashboard portálem? Co je to mashup aplikace? Mohl/mohla byste uvést nějaký příklad? Co mají společného mashup aplikace s integračními službami?</t>
-  </si>
-  <si>
-    <t>Sdílení dat mezi aplikacemi/IS</t>
-  </si>
-  <si>
-    <t>Definujte jednotlivé úrovně propojení aplikací dle způsobu sdílení dat (začít můžete od sdílení souborů přenášených na paměťových médiích). Co jsou to relační databáze? Čím se liší relační databáze od dokumentové NoSQL databáze?</t>
-  </si>
-  <si>
     <t>Vyhledatelnost dokumentů</t>
   </si>
   <si>
-    <t>S jakými základními typy dokumentů lze rozlišovat? Jakými metadami lze charakterizovat článek v odborném časopise? Co jsou to klíčová slova? Jak je lze u dokumentu stanovit? Co je to MDT a JEL klasifikace? Proč je potřeba u převzatých myšlenek odkazovat na původní zdroje?</t>
-  </si>
-  <si>
     <t>JSON</t>
   </si>
   <si>
@@ -216,56 +108,74 @@
     <t>Stručně popište formáty XML a JSON. Znáte nějaké další strukturované datové formáty? Je HTML strukturovaným formátem? K jakému účelu se strukturované datové formáty používají? Lze všechny typy informací popisovat strukturovanými formáty?</t>
   </si>
   <si>
-    <t>Charakterizujte SOA. Co je to IT služba? Jaké jsou motivace k využívání služeb a jaká jsou naopak rizika? Jaké vlastnosti služby by nás měly zajímat? Co je to SLA?</t>
-  </si>
-  <si>
-    <t>Jaké jsou základní vlastnosti IT služeb? Co je to autonomie a bezstavovost služby? Lze omezit, kdo bude moci konkrétní službu využívat? Najděte nějaký příklad SaaS.</t>
-  </si>
-  <si>
     <t>Metadata na internetu, SEO</t>
   </si>
   <si>
-    <t>Jaká metadat se na používají u webových stránek? K čemu tato metadata slouží? Co jsou to sémantická data na webu a co mají společného s schema.org? Jakými metodami lze zlepšit pozici stránky ve vyhledávači?</t>
-  </si>
-  <si>
-    <t>Jaký je vztah dat, informací a znalostí? Mají informace a znalosti nějakou hodnotu? Čím se zabývá znalostní management? Uveďte příklad strukturovaných a nestrukturovaných dat zpracovávaných ve firmách.</t>
-  </si>
-  <si>
-    <t>Data a znalosti, znalostní management</t>
-  </si>
-  <si>
     <t>RPC - REST - GraphQL</t>
   </si>
   <si>
-    <t>Popište základní myšlenkový koncept fungování těchto typů API a uveďte příklad jejich praktického využití. Může aplikace poskytovat více různých API najednou?</t>
-  </si>
-  <si>
     <t>Student(ka)</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Jaký je rozdíl mezi licencovaným a volně dostupným zdrojem? Co je to autentizace a autorizace uživatelů? Jakými způsoby lze omezit přístup ke zdroji jen pro konkrétní uživatele? Co je to protokol OAuth a kde se používá?</t>
-  </si>
-  <si>
-    <t>Proč se vlastně bavit o JSON:API či OData, když bychom mohli říct, že jde prostě o REST? V čem se tyto specifikace odlišují? Pokuste se najít příklad použití protokolu OData.</t>
-  </si>
-  <si>
-    <t>JSON:API, OData</t>
-  </si>
-  <si>
     <t>Prototypování a dokumentování API</t>
   </si>
   <si>
-    <t>Jakým způsobem se obvykle popisuje struktura (požadavky, zasílaná data) základních typů API? Stručně popište možnosti popisu struktury u SOAP, REST a GraphQL API. K čemu je vhodné/použitelné prototypování API? Podařilo by se Vám najít nějaý vhodný nástroj pro prototypování REST API?</t>
+    <t>Co je to API? Popište základní myšlenkový koncept fungování těchto typů API a uveďte příklad jejich praktického využití. Může aplikace poskytovat více různých API najednou?</t>
+  </si>
+  <si>
+    <t>Prototypování REST API, JSON:API, Odata</t>
+  </si>
+  <si>
+    <t>Jakým způsobem se obvykle popisuje struktura (požadavky, zasílaná data) základních typů API? Stručně popište možnosti popisu struktury u SOAP, REST a GraphQL API. K čemu je vhodné/použitelné prototypování API? Podařilo by se Vám najít nějaký vhodný nástroj pro prototypování REST API?</t>
+  </si>
+  <si>
+    <t>Jaké nástroje se používají pro dokumentaci a pro prototypování REST API? K čemu je vlastně dobré vytvářet prototyp REST API? Charakterizujte JSON:API nebo OData, jeho vlastnosti a použití. Čím se liší JSON:API či OData od obecného REST API?</t>
+  </si>
+  <si>
+    <t>Co jsou to grafová data? Jaký je vztah grafových dat a GraphQL? Je možné najít grafová data např. na Facebooku? Lze se dotazovat na grafová data přes REST API? Lze ukládat grafová data v relačních a NoSQL databázích?</t>
+  </si>
+  <si>
+    <t>Jaké jsou výhody a nevýhody jednotlivých variant uložení dat? V jakých formátech se obvykle sdílejí data v prostředí internetu? Jak poznat relevantní informační zdroj? Mají informace a znalosti nějakou hodnotu?</t>
+  </si>
+  <si>
+    <t>K čemu se používají metadata? Jaký je vztah dat a metadat? Charakterizujte metadata informačních zdrojů. Co knihovny obvykle označují jako "elektronické informační zdroje"? Jakým způsobem lze popsat dokumenty zpracovávané knihovnami? Mají nějaká metadata také konkrétní dokumenty?</t>
+  </si>
+  <si>
+    <t>XML-RPC, SOAP, gRPC</t>
+  </si>
+  <si>
+    <t>Co je to XML-RPC? Co je to SOAP a k čemu se používá? Zvládl(a) byste najít nějaký příklad použití tohoto typu API? Jakým způsobem lze dokumentovat API tohoto typu? Co je to gRPC a jaké jsou jeho základní vlastnosti?</t>
+  </si>
+  <si>
+    <t>Lze najít API i v aplikacích, které mají vlastní uživatelské rozhraní? K čemu se používají integrační služby? Vyberte si nějakou integrační službu a popište její vlastnosti a nějaké vhodné příklady použití. Lze využít integrační služby pro automatizaci smart elektroniky?</t>
+  </si>
+  <si>
+    <t>Jaká metadat se na používají u webových stránek? K čemu tato metadata slouží? Co jsou to sémantická data na webu a co mají společného s schema.org? Jakými metodami lze zlepšit pozici stránky ve vyhledávači? Co je to OpenGraph? Uveďte příklady použití.</t>
+  </si>
+  <si>
+    <t>Jaký je vztah dat, informací a znalostí? Co jsou to explicitní a tacitní znalosti? Lze znalosti někde shromažďovat a nějak je sdílet a prohledávat? Mají informace a znalosti nějakou hodnotu? Je výhodnější ukládat data v databázích nebo v jednotlivých souborech?</t>
+  </si>
+  <si>
+    <t>S jakými základními typy dokumentů lze rozlišovat? Jakými metadami lze charakterizovat článek v odborném časopise? Co jsou to klíčová slova? Jak je lze u dokumentu stanovit? Co je to MDT a JEL klasifikace? Proč je potřeba u převzatých myšlenek odkazovat na původní zdroje?  Co jsou to primární, sekundární a terciání informace?</t>
+  </si>
+  <si>
+    <t>Co je to portál? Uveďte příklad portálů. Co zajišťuje portál pro jednotlivé portlety? Je každý dashboard portálem? Co je to mashup aplikace? Mohl/mohla byste uvést nějaký příklad? Co mají společného mashup aplikace s integračními službami? Jakými způsoby lze omezit přístup k informačnímu zdroji/aplikaci jen pro konkrétní uživatele?</t>
+  </si>
+  <si>
+    <t>Portály, mashup aplikace, přístup uživatelů</t>
+  </si>
+  <si>
+    <t>Otázka</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,6 +188,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -310,11 +228,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -629,17 +549,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A274E4-31AD-4CF7-B5B8-1A1802800CC0}">
-  <dimension ref="A1:D36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="59.85546875" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="59.81640625" customWidth="1"/>
+    <col min="4" max="4" width="26.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -648,503 +569,303 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
         <v>25</v>
       </c>
+      <c r="C4" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="D4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
       <c r="D22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="1"/>
       <c r="D23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" t="s">
-        <v>64</v>
-      </c>
-      <c r="D32" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E36">
-    <sortCondition descending="1" ref="E2:E36"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
